--- a/Compititor's_Price/Celotex_Prices/Celotex_Prices_08-03-2026.xlsx
+++ b/Compititor's_Price/Celotex_Prices/Celotex_Prices_08-03-2026.xlsx
@@ -1376,7 +1376,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>£27.95</t>
+          <t>Error: HTTPSConnectionPool(host='www.insulationsuperstore.co.uk', port=443): Read timed out. (read timeout=30)</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
